--- a/input/api/Archieve/ECLIPSE_Account Dashboard_Loan_DDD_API_Design_v1_Workshop.xlsx
+++ b/input/api/Archieve/ECLIPSE_Account Dashboard_Loan_DDD_API_Design_v1_Workshop.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30327"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apcdeloitte.sharepoint.com/sites/MBBNGA/Shared Documents/General/03 Design/02. Domain Design/ECLIPSE/DDD/Journey/Account Dashboard - Loan Financing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://apcdeloitte.sharepoint.com/sites/MBBNGA/Shared Documents/General/03 Design/02. Domain Design/03. ECLIPSE/DDD/Journey/Account Dashboard - Loan Financing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9982" documentId="13_ncr:1_{6E9508CF-76A0-4022-8E2E-8A46CAF28EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E15ECE5-32F0-4216-A13D-1F1458BBCC39}"/>
+  <xr:revisionPtr revIDLastSave="9985" documentId="13_ncr:1_{6E9508CF-76A0-4022-8E2E-8A46CAF28EBC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5628892C-1CE2-42E4-B195-BA4BA276F403}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="837" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14340" yWindow="-16200" windowWidth="14610" windowHeight="15585" tabRatio="837" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="33" r:id="rId1"/>
@@ -42,17 +42,23 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="269" uniqueCount="113">
   <si>
     <t>No</t>
   </si>
   <si>
+    <t xml:space="preserve">Sheet Name </t>
+  </si>
+  <si>
     <t>API Name</t>
   </si>
   <si>
     <t>Method</t>
   </si>
   <si>
+    <t xml:space="preserve">Microservice Ownership </t>
+  </si>
+  <si>
     <t>Endpoint</t>
   </si>
   <si>
@@ -62,164 +68,100 @@
     <t>Remarks</t>
   </si>
   <si>
+    <t>1.1 Loan Dashboard - Landing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan dashboard </t>
+  </si>
+  <si>
     <t>GET</t>
   </si>
   <si>
-    <t xml:space="preserve">Loan dashboard </t>
-  </si>
-  <si>
-    <t>1.1 Loan Dashboard - Landing</t>
+    <t xml:space="preserve">dep-dashboard </t>
+  </si>
+  <si>
+    <t>/v1/external/accounts?accountGroup={accountGroup}</t>
+  </si>
+  <si>
+    <t>info-loan</t>
+  </si>
+  <si>
+    <t>/v1/internal/accounts/summary</t>
+  </si>
+  <si>
+    <t>ESB_API_Spec_AccountInfo_v2.8 -&gt; AccountSummary_CASA_CC</t>
+  </si>
+  <si>
+    <t>1.2 Personal Loan Acc
+1.2.4 PL Shariah Acc
+1.3 Auto Loan Acc
+1.3.1 Auto Loan Shariah
+1.4 Mortgage Loan Acc
+1.4.1 Mortgage Loan Shariah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan transaction history </t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pending ESB Spec </t>
+  </si>
+  <si>
+    <t>1.2.1 View All Trans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">View all transaction history </t>
   </si>
   <si>
     <t xml:space="preserve">GET </t>
   </si>
   <si>
-    <t>1.2.1 View All Trans</t>
-  </si>
-  <si>
-    <t>Add loan nickname</t>
-  </si>
-  <si>
-    <t>POST</t>
-  </si>
-  <si>
-    <t>PATCH</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Screen </t>
-  </si>
-  <si>
-    <t>User Action</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Business Logic </t>
-  </si>
-  <si>
-    <t>Microservice Ownership</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Request JSON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Success Response JSON </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Failed Response JSON </t>
-  </si>
-  <si>
-    <t>ESB</t>
-  </si>
-  <si>
-    <t>Eclipse DB</t>
-  </si>
-  <si>
-    <t>Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BE Validation </t>
-  </si>
-  <si>
-    <t>N/A</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Y </t>
-  </si>
-  <si>
-    <t>User tap "View all transactions" hyperlink</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>"View All Transaction with Searching" rule
-a. The system shall support search functionality for YTD+24 data, where results are filtered and displayed from the loaded YTD+24 data pool upon user search input, , with records presented in folds of 20 and progressively expanded on scroll when more than 20 matches are found
-b. Once all matching records have been rendered, an “End of List” marker shall be displayed, and further scrolling beyond that point shall be disabled.</t>
-  </si>
-  <si>
-    <t>User tap "Filter" -&gt; click "Apply"</t>
-  </si>
-  <si>
-    <t>"View All Transaction with Filter" rule
-a. Transaction history results can be filtered by the following categories: Transaction type, transaction amount, time range
-b. Users may apply one or multiple categories simultaneously.
-c. Upon tapping [Clear], the system will reapply the filter and display matching results from the YTD+24 data; results are presented in folds of 20  in batches of 20 and progressively expanded on scroll when more than 20 matches are found
-d. Once all records have been displayed, an “End of List” marker will appear, and further scrolling will be disabled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User tap "Summary" tab </t>
-  </si>
-  <si>
-    <t xml:space="preserve">User add nickname </t>
-  </si>
-  <si>
-    <t xml:space="preserve">User update nickname </t>
-  </si>
-  <si>
-    <t xml:space="preserve">When user tap "Loan/Financing" tab and screen is loaded </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microservice Ownership </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan transaction history </t>
-  </si>
-  <si>
-    <t xml:space="preserve">View all transaction history </t>
-  </si>
-  <si>
-    <t xml:space="preserve">N </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Transactions
-a. List of transactions to group based on date
-     - If Today's Date, display as "Today"
-     - Otherwise, display the date accordingly 
-b.  Only 10 row of transactions to display in descending date order 
-c. "View All Transactions" button will only be shown if there are more than 10 transactions (based on the latest of YTD + 24 months data) to display </t>
-    </r>
+    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions?startDate={startDate}&amp;endDate={endDate}&amp;page={page}&amp;limit={limit}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search all transaction history </t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions/search?startDate={startDate}&amp;endDate={endDate}&amp;keyword={keyword}&amp;page={page}&amp;limit={limit}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Introduce feature flag to turn on or off for this function. Searching rule is only achievable when CDC come in </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Filter transaction history </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Export transaction history </t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/statement?statementType={statementType}&amp;statementFormat={statementFormat}</t>
+  </si>
+  <si>
+    <t>1.2.2 PL Convent Summary
+1.2.5 PL Shariah Summary
+1.3 Auto Loan Acc
+1.3.1 Auto Loan Shariah
+1.4 Mortgage Loan Acc
+1.4.1 Mortgage Loan Shariah</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan detail </t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/detail</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <sz val="11"/>
-        <color rgb="FFFF0000"/>
+        <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>[HOST will keep up to YTD+24months data ? ]</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-     - Upon clicked on [View All Transactions], user will be navigated to Transaction History screen. Refer to next worksheet tab for more info
-d. It shall not be displayed in the transaction list if it is older than YTD + 24 months data
-e. To display the transaction data that comply with Tier 1 format
-f. To retrieve all types of transaction available</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">User key in keyword at Search </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Export transaction history </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Search all transaction history </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Summary Tab Behaviour 
-a. The Summary tab shall only display read-only information
-b. No editing functionality shall be available on this screen
+      <t xml:space="preserve">ESB_API_Spec_AccountInfo_v2.8 -&gt; Account Balance Details 
 </t>
     </r>
     <r>
@@ -230,79 +172,85 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve">- (PL, AL) Auto Debit Account - Account Name
-- (PL, AL) Auto Debit Account - Account Number
-- (PL) Maturity date
-</t>
+      <t xml:space="preserve">Pending discussion for the the missing fields </t>
     </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">- (AL) Registered vehicle plate number - CLS don't have this information </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-- (PL, AL, ML) Late penalty
-- (ML) Signing date
-- (PL, AL, ML) Next payment date 
-- (PL, AL, ML) Principal amount </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan detail </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ECLIPSE DB:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1. account_nickname </t>
-    </r>
+  </si>
+  <si>
+    <t>1.2.3 PL Convent Manage
+1.2.6 PL Shariah Manage
+1.3 Auto Loan Acc
+1.3.1 Auto Loan Shariah
+1.4 Mortgage Loan Acc
+1.4.1 Mortgage Loan Shariah</t>
+  </si>
+  <si>
+    <t>Add loan nickname</t>
+  </si>
+  <si>
+    <t>POST</t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/nickname</t>
+  </si>
+  <si>
+    <t>Update loan nickname</t>
+  </si>
+  <si>
+    <t>PATCH</t>
+  </si>
+  <si>
+    <t>Delete loan nickname</t>
+  </si>
+  <si>
+    <t>DELETE</t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/{accountId}/nickname</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Screen </t>
+  </si>
+  <si>
+    <t>User Action</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Logic </t>
+  </si>
+  <si>
+    <t>Microservice Ownership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Request JSON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Success Response JSON </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Failed Response JSON </t>
+  </si>
+  <si>
+    <t>ESB</t>
+  </si>
+  <si>
+    <t>Eclipse DB</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Note </t>
   </si>
   <si>
     <t>On user load of account dashboard, content used to get account dashboard menu settings</t>
   </si>
   <si>
+    <t>N/A</t>
+  </si>
+  <si>
     <t>CMS</t>
   </si>
   <si>
     <t>/cms/api/module/account-dashboard</t>
-  </si>
-  <si>
-    <t>On user load of account dashboard, content used to get app translation</t>
-  </si>
-  <si>
-    <t>/cms/api/i18n-content/account-dashboard</t>
-  </si>
-  <si>
-    <t>MBB UI/UX Team</t>
   </si>
   <si>
     <t>{
@@ -419,29 +367,35 @@
 }</t>
   </si>
   <si>
-    <t xml:space="preserve">User tap one of the account at Loan/Financing tab </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loan header FE render from the previous screen response which is Loan/Financing tab </t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">The loan account details will be displayed upon successfully retrieved data via host integration, and it will be </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>defaulted pointing to Transactions tab</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Note </t>
+    <t>{
+  "status": 500,
+  "message": "Request processed failed",
+  "timestamp": "2026-01-13T12:00:00",
+  "correlationId": "abc123-correlation-id",
+}</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>On user load of account dashboard, content used to get app translation</t>
+  </si>
+  <si>
+    <t>/cms/api/i18n-content/account-dashboard</t>
+  </si>
+  <si>
+    <t>MBB UI/UX Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">When user tap "Loan/Financing" tab and screen is loaded </t>
+  </si>
+  <si>
+    <t>getDashboard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/v1/external/accounts?featureType={featureType}
+example : /v1/external/accounts?featureType=DASHBOARD_LOAN
+</t>
   </si>
   <si>
     <t>{
@@ -505,20 +459,104 @@
 }</t>
   </si>
   <si>
-    <t>{
-  "status": 500,
-  "message": "Request processed failed",
-  "timestamp": "2026-01-13T12:00:00",
-  "correlationId": "abc123-correlation-id",
-}</t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">/v1/external/accounts?accountGroup={accountGroup}
-example : /v1/external/accounts?accountGroup=LOAN
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Y </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>ESB:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> 
+ESB_API_Spec_AccountInfo_v2.8 -&gt; AccountSummary_CASA_CC
 </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">ECLIPSE DB:  
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1. account_nickname
+2. product_catalog</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">BE Validation: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Either request param accountGroup or accountType is mandatory</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User tap one of the account at Loan/Financing tab </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loan header FE render from the previous screen response which is Loan/Financing tab </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">The loan account details will be displayed upon successfully retrieved data via host integration, and it will be </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>defaulted pointing to Transactions tab</t>
+    </r>
   </si>
   <si>
     <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions
@@ -590,6 +628,13 @@
 }</t>
   </si>
   <si>
+    <t xml:space="preserve">N </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESB: 
+ESB_API_Spec_AccountInfo_v2.8 -&gt; Account Balance Details </t>
+  </si>
+  <si>
     <t>Flow: FE -&gt; ECLIPSE LAYER 
 1. erp-casa -&gt; esb
 BE Validation: 
@@ -601,28 +646,41 @@
 2. If accountStatus = CLOSED, FE display closed loan text banner with message "Account view ends in 90 days. Ensure you have saved all necessary details before it is removed from the dashboard."</t>
   </si>
   <si>
-    <t xml:space="preserve">Sheet Name </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pending ESB Spec </t>
-  </si>
-  <si>
-    <t>/v1/internal/accounts/summary</t>
-  </si>
-  <si>
-    <t>ESB_API_Spec_AccountInfo_v2.8 -&gt; AccountSummary_CASA_CC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Filter transaction history </t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions?startDate={startDate}&amp;endDate={endDate}&amp;page={page}&amp;limit={limit}</t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions/search?startDate={startDate}&amp;endDate={endDate}&amp;keyword={keyword}&amp;page={page}&amp;limit={limit}</t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/statement?statementType={statementType}&amp;statementFormat={statementFormat}</t>
+    <t>User tap "View all transactions" hyperlink</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Transactions
+a. List of transactions to group based on date
+     - If Today's Date, display as "Today"
+     - Otherwise, display the date accordingly 
+b.  Only 10 row of transactions to display in descending date order 
+c. "View All Transactions" button will only be shown if there are more than 10 transactions (based on the latest of YTD + 24 months data) to display </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>[HOST will keep up to YTD+24months data ? ]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+     - Upon clicked on [View All Transactions], user will be navigated to Transaction History screen. Refer to next worksheet tab for more info
+d. It shall not be displayed in the transaction list if it is older than YTD + 24 months data
+e. To display the transaction data that comply with Tier 1 format
+f. To retrieve all types of transaction available</t>
+    </r>
   </si>
   <si>
     <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions?startDate={startDate}&amp;endDate={endDate}&amp;page={page}&amp;limit={limit}
@@ -643,13 +701,6 @@
       </rPr>
       <t>Pending API SPEC</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Introduce feature flag to turn on or off for this function. Searching rule is only achievable when CDC come in </t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions/search?startDate={startDate}&amp;endDate={endDate}&amp;keyword={keyword}&amp;page={page}&amp;limit={limit}
-example : /v1/external/accounts/account-type/PL/account-id/514013314526/transactions?startDate="2025-01-01"&amp;endDate="2025-05-25"&amp;keyword="testing"&amp;page=0&amp;limit=10</t>
   </si>
   <si>
     <r>
@@ -674,6 +725,18 @@
       <t xml:space="preserve">
 1. Validate account ID belongs to customer based on token</t>
     </r>
+  </si>
+  <si>
+    <t xml:space="preserve">User key in keyword at Search </t>
+  </si>
+  <si>
+    <t>"View All Transaction with Searching" rule
+a. The system shall support search functionality for YTD+24 data, where results are filtered and displayed from the loaded YTD+24 data pool upon user search input, , with records presented in folds of 20 and progressively expanded on scroll when more than 20 matches are found
+b. Once all matching records have been rendered, an “End of List” marker shall be displayed, and further scrolling beyond that point shall be disabled.</t>
+  </si>
+  <si>
+    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/transactions/search?startDate={startDate}&amp;endDate={endDate}&amp;keyword={keyword}&amp;page={page}&amp;limit={limit}
+example : /v1/external/accounts/account-type/PL/account-id/514013314526/transactions?startDate="2025-01-01"&amp;endDate="2025-05-25"&amp;keyword="testing"&amp;page=0&amp;limit=10</t>
   </si>
   <si>
     <r>
@@ -712,6 +775,59 @@
     </r>
   </si>
   <si>
+    <t>User tap "Filter" -&gt; click "Apply"</t>
+  </si>
+  <si>
+    <t>"View All Transaction with Filter" rule
+a. Transaction history results can be filtered by the following categories: Transaction type, transaction amount, time range
+b. Users may apply one or multiple categories simultaneously.
+c. Upon tapping [Clear], the system will reapply the filter and display matching results from the YTD+24 data; results are presented in folds of 20  in batches of 20 and progressively expanded on scroll when more than 20 matches are found
+d. Once all records have been displayed, an “End of List” marker will appear, and further scrolling will be disabled.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Introduce feature flag to turn off Money in/out filteration. Only achievable when CDC come in </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">BE Validation: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+1. Validate account ID belongs to customer based on token
+</t>
+    </r>
+  </si>
+  <si>
     <t xml:space="preserve">User click [Export Transaction]
 1. Send to email </t>
   </si>
@@ -740,6 +856,56 @@
   },
   "link": {}
 }</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BE Validation </t>
+  </si>
+  <si>
+    <t xml:space="preserve">User tap "Summary" tab </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Summary Tab Behaviour 
+a. The Summary tab shall only display read-only information
+b. No editing functionality shall be available on this screen
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- (PL, AL) Auto Debit Account - Account Name
+- (PL, AL) Auto Debit Account - Account Number
+- (PL) Maturity date
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">- (AL) Registered vehicle plate number - CLS don't have this information </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+- (PL, AL, ML) Late penalty
+- (ML) Signing date
+- (PL, AL, ML) Next payment date 
+- (PL, AL, ML) Principal amount </t>
+    </r>
   </si>
   <si>
     <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/detail
@@ -830,217 +996,6 @@
 }</t>
   </si>
   <si>
-    <t>/v1/external/accounts/account-type/{accountType}/account-id/{accountId}/detail</t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/nickname</t>
-  </si>
-  <si>
-    <t>{
-  "accountId": "504233415671",
-  "nickname": "MUTHU"
-}</t>
-  </si>
-  <si>
-    <t>{
-  "status": 200,
-  "message": "add_nickname_success",
-  "timestamp": "2026-01-13T12:00:00",
-  "correlationId": "abc123-correlation-id",
-  "meta": {
-    "provider": "erp"
-  }
-}</t>
-  </si>
-  <si>
-    <t>{
-  "status": 200,
-  "message": "update_nickname_success",
-  "timestamp": "2026-01-13T12:00:00",
-  "correlationId": "abc123-correlation-id",
-  "meta": {
-    "provider": "erp"
-  }
-}</t>
-  </si>
-  <si>
-    <t>1.2 Personal Loan Acc
-1.2.4 PL Shariah Acc
-1.3 Auto Loan Acc
-1.3.1 Auto Loan Shariah
-1.4 Mortgage Loan Acc
-1.4.1 Mortgage Loan Shariah</t>
-  </si>
-  <si>
-    <t>1.2.2 PL Convent Summary
-1.2.5 PL Shariah Summary
-1.3 Auto Loan Acc
-1.3.1 Auto Loan Shariah
-1.4 Mortgage Loan Acc
-1.4.1 Mortgage Loan Shariah</t>
-  </si>
-  <si>
-    <t>1.2.3 PL Convent Manage
-1.2.6 PL Shariah Manage
-1.3 Auto Loan Acc
-1.3.1 Auto Loan Shariah
-1.4 Mortgage Loan Acc
-1.4.1 Mortgage Loan Shariah</t>
-  </si>
-  <si>
-    <t>/v1/external/accounts?accountGroup={accountGroup}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">BE Validation: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Either request param accountGroup or accountType is mandatory</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Introduce feature flag to turn off Money in/out filteration. Only achievable when CDC come in </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">BE Validation: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Validate account ID belongs to customer based on token
-</t>
-    </r>
-  </si>
-  <si>
-    <t>Update loan nickname</t>
-  </si>
-  <si>
-    <t>Delete loan nickname</t>
-  </si>
-  <si>
-    <t>DELETE</t>
-  </si>
-  <si>
-    <t>/v1/external/accounts/{accountId}/nickname</t>
-  </si>
-  <si>
-    <t xml:space="preserve">User delete nickname </t>
-  </si>
-  <si>
-    <t xml:space="preserve">addNickname </t>
-  </si>
-  <si>
-    <t xml:space="preserve">updateNickname </t>
-  </si>
-  <si>
-    <t xml:space="preserve">deleteNickname </t>
-  </si>
-  <si>
-    <t>{
-  "status": 200,
-  "message": "delete_nickname_success",
-  "timestamp": "2026-01-13T12:00:00",
-  "correlationId": "abc123-correlation-id",
-  "meta": {
-    "provider": "erp"
-  }
-}</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ECLIPSE DB:
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">1. account_nickname </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">BE Validation: </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">
-1. Validate account ID belongs to customer based on token</t>
-    </r>
-  </si>
-  <si>
     <r>
       <rPr>
         <b/>
@@ -1088,6 +1043,29 @@
     </r>
   </si>
   <si>
+    <t xml:space="preserve">User add nickname </t>
+  </si>
+  <si>
+    <t xml:space="preserve">addNickname </t>
+  </si>
+  <si>
+    <t>{
+  "accountId": "504233415671",
+  "nickname": "MUTHU"
+}</t>
+  </si>
+  <si>
+    <t>{
+  "status": 200,
+  "message": "add_nickname_success",
+  "timestamp": "2026-01-13T12:00:00",
+  "correlationId": "abc123-correlation-id",
+  "meta": {
+    "provider": "erp"
+  }
+}</t>
+  </si>
+  <si>
     <r>
       <rPr>
         <b/>
@@ -1097,30 +1075,7 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>ESB:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> 
-ESB_API_Spec_AccountInfo_v2.8 -&gt; AccountSummary_CASA_CC
-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ECLIPSE DB:  
+      <t xml:space="preserve">ECLIPSE DB:
 </t>
     </r>
     <r>
@@ -1131,49 +1086,49 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>1. account_nickname
-2. product_catalog</t>
+      <t xml:space="preserve">1. account_nickname </t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">ESB_API_Spec_AccountInfo_v2.8 -&gt; Account Balance Details 
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">Pending discussion for the the missing fields </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">ESB: 
-ESB_API_Spec_AccountInfo_v2.8 -&gt; Account Balance Details </t>
-  </si>
-  <si>
-    <t xml:space="preserve">dep-dashboard </t>
-  </si>
-  <si>
-    <t>info-loan</t>
+    <t xml:space="preserve">User update nickname </t>
+  </si>
+  <si>
+    <t xml:space="preserve">updateNickname </t>
+  </si>
+  <si>
+    <t>{
+  "status": 200,
+  "message": "update_nickname_success",
+  "timestamp": "2026-01-13T12:00:00",
+  "correlationId": "abc123-correlation-id",
+  "meta": {
+    "provider": "erp"
+  }
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User delete nickname </t>
+  </si>
+  <si>
+    <t xml:space="preserve">deleteNickname </t>
+  </si>
+  <si>
+    <t>{
+  "status": 200,
+  "message": "delete_nickname_success",
+  "timestamp": "2026-01-13T12:00:00",
+  "correlationId": "abc123-correlation-id",
+  "meta": {
+    "provider": "erp"
+  }
+}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1517,6 +1472,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1527,12 +1488,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1635,8 +1590,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="395357" y="394591"/>
-          <a:ext cx="1600200" cy="3651995"/>
+          <a:off x="381000" y="393349"/>
+          <a:ext cx="1600200" cy="3636948"/>
           <a:chOff x="328789" y="240594"/>
           <a:chExt cx="1600200" cy="4923753"/>
         </a:xfrm>
@@ -1772,8 +1727,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="368300" y="342900"/>
-          <a:ext cx="1828800" cy="4438650"/>
+          <a:off x="355600" y="520700"/>
+          <a:ext cx="1828800" cy="4432300"/>
           <a:chOff x="387350" y="704850"/>
           <a:chExt cx="1828800" cy="4279900"/>
         </a:xfrm>
@@ -1904,8 +1859,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2343150" y="336550"/>
-          <a:ext cx="1962150" cy="4591050"/>
+          <a:off x="2330450" y="514350"/>
+          <a:ext cx="1962150" cy="4584700"/>
           <a:chOff x="2432050" y="742950"/>
           <a:chExt cx="2012950" cy="4184650"/>
         </a:xfrm>
@@ -2707,8 +2662,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="2795410" y="473074"/>
-          <a:ext cx="1883720" cy="4180641"/>
+          <a:off x="2784121" y="651580"/>
+          <a:ext cx="1883720" cy="4185932"/>
           <a:chOff x="2795410" y="473074"/>
           <a:chExt cx="1883720" cy="4180641"/>
         </a:xfrm>
@@ -2958,8 +2913,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="611364" y="373944"/>
-          <a:ext cx="1688747" cy="3788834"/>
+          <a:off x="600075" y="371475"/>
+          <a:ext cx="1688747" cy="3769078"/>
           <a:chOff x="611364" y="373944"/>
           <a:chExt cx="1688747" cy="3788834"/>
         </a:xfrm>
@@ -3317,11 +3272,11 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="2" max="2" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="29" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.453125" customWidth="1"/>
+    <col min="4" max="4" width="28.42578125" customWidth="1"/>
   </cols>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3334,283 +3289,283 @@
     <tabColor theme="7"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.81640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.36328125" style="22" customWidth="1"/>
-    <col min="3" max="3" width="44.1796875" style="22" customWidth="1"/>
-    <col min="4" max="4" width="15.1796875" style="22" customWidth="1"/>
-    <col min="5" max="5" width="23.90625" style="22" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.28515625" style="22" customWidth="1"/>
+    <col min="3" max="3" width="44.28515625" style="22" customWidth="1"/>
+    <col min="4" max="4" width="15.28515625" style="22" customWidth="1"/>
+    <col min="5" max="5" width="23.85546875" style="22" customWidth="1"/>
     <col min="6" max="6" width="88" style="22" customWidth="1"/>
-    <col min="7" max="7" width="8.81640625" style="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="57.90625" style="22" customWidth="1"/>
-    <col min="9" max="16384" width="8.81640625" style="22"/>
+    <col min="7" max="7" width="8.7109375" style="22" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57.85546875" style="22" customWidth="1"/>
+    <col min="9" max="16384" width="8.7109375" style="22"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>66</v>
+        <v>1</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="14" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" ht="13.9" customHeight="1">
       <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="34" t="s">
-        <v>7</v>
+      <c r="C2" s="36" t="s">
+        <v>9</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>94</v>
+        <v>12</v>
       </c>
       <c r="G2" s="10"/>
       <c r="H2" s="10"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8">
       <c r="A3" s="13">
         <v>2</v>
       </c>
-      <c r="B3" s="35"/>
-      <c r="C3" s="35"/>
+      <c r="B3" s="37"/>
+      <c r="C3" s="37"/>
       <c r="D3" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="G3" s="10"/>
       <c r="H3" s="13" t="s">
-        <v>69</v>
+        <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" ht="86.45">
       <c r="A4" s="13">
         <v>3</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>91</v>
+        <v>16</v>
       </c>
       <c r="C4" s="13" t="s">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="D4" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F4" s="13" t="s">
-        <v>61</v>
+        <v>18</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="23" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" ht="28.9">
       <c r="A5" s="13">
         <v>4</v>
       </c>
-      <c r="B5" s="34" t="s">
-        <v>10</v>
+      <c r="B5" s="36" t="s">
+        <v>20</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="D5" s="13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G5" s="13"/>
       <c r="H5" s="23" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" ht="43.15">
       <c r="A6" s="13">
         <v>5</v>
       </c>
-      <c r="B6" s="36"/>
+      <c r="B6" s="38"/>
       <c r="C6" s="13" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="D6" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>72</v>
+        <v>25</v>
       </c>
       <c r="G6" s="13"/>
       <c r="H6" s="33" t="s">
-        <v>76</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" ht="28.9">
       <c r="A7" s="13">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
+      <c r="B7" s="38"/>
       <c r="C7" s="13" t="s">
-        <v>70</v>
+        <v>27</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>71</v>
+        <v>23</v>
       </c>
       <c r="G7" s="13"/>
       <c r="H7" s="23" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="29" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" ht="28.9">
       <c r="A8" s="13">
         <v>7</v>
       </c>
-      <c r="B8" s="36"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="13" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>73</v>
+        <v>29</v>
       </c>
       <c r="G8" s="13"/>
       <c r="H8" s="23" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="87" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" ht="86.45">
       <c r="A9" s="13">
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>92</v>
+        <v>30</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F9" s="13" t="s">
-        <v>86</v>
+        <v>32</v>
       </c>
       <c r="G9" s="13"/>
       <c r="H9" s="13" t="s">
-        <v>110</v>
+        <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="87" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" ht="87" customHeight="1">
       <c r="A10" s="24">
         <v>9</v>
       </c>
-      <c r="B10" s="37" t="s">
-        <v>93</v>
+      <c r="B10" s="39" t="s">
+        <v>34</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="D10" s="30" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:8" ht="91.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" ht="91.5" customHeight="1">
       <c r="A11" s="24">
         <v>10</v>
       </c>
-      <c r="B11" s="37"/>
+      <c r="B11" s="39"/>
       <c r="C11" s="24" t="s">
-        <v>97</v>
+        <v>38</v>
       </c>
       <c r="D11" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="E11" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E11" s="13" t="s">
-        <v>113</v>
-      </c>
       <c r="F11" s="24" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="G11" s="24"/>
       <c r="H11" s="24"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8">
       <c r="A12" s="25">
         <v>11</v>
       </c>
-      <c r="B12" s="37"/>
+      <c r="B12" s="39"/>
       <c r="C12" s="24" t="s">
-        <v>98</v>
+        <v>40</v>
       </c>
       <c r="D12" s="32" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="G12" s="25"/>
       <c r="H12" s="25"/>
@@ -3632,183 +3587,185 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.453125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="44" customWidth="1"/>
-    <col min="3" max="3" width="57.54296875" customWidth="1"/>
-    <col min="4" max="4" width="76.1796875" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" customWidth="1"/>
-    <col min="6" max="6" width="29.08984375" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="48.36328125" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="70.453125" customWidth="1"/>
-    <col min="11" max="11" width="45.81640625" customWidth="1"/>
-    <col min="12" max="12" width="4.1796875" customWidth="1"/>
-    <col min="13" max="13" width="12.6328125" customWidth="1"/>
-    <col min="14" max="14" width="32.81640625" customWidth="1"/>
+    <col min="3" max="3" width="57.5703125" customWidth="1"/>
+    <col min="4" max="4" width="76.28515625" customWidth="1"/>
+    <col min="5" max="5" width="13.5703125" customWidth="1"/>
+    <col min="6" max="6" width="29.140625" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="48.28515625" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="70.42578125" customWidth="1"/>
+    <col min="11" max="11" width="45.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" customWidth="1"/>
+    <col min="14" max="14" width="32.7109375" customWidth="1"/>
     <col min="15" max="15" width="61" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" ht="93.4" customHeight="1">
+      <c r="A2" s="35">
         <v>1</v>
       </c>
-      <c r="F1" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="G1" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="H1" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" ht="93.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39">
-        <v>1</v>
-      </c>
-      <c r="B2" s="38"/>
+      <c r="B2" s="34"/>
       <c r="C2" s="6" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E2" s="16"/>
       <c r="F2" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G2" s="16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" s="17" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="16" t="s">
-        <v>29</v>
-      </c>
       <c r="M2" s="16" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
     </row>
-    <row r="3" spans="1:15" ht="87" x14ac:dyDescent="0.35">
-      <c r="A3" s="39"/>
-      <c r="B3" s="38"/>
+    <row r="3" spans="1:15" ht="86.45">
+      <c r="A3" s="35"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="19" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="E3" s="16"/>
       <c r="F3" s="16" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="G3" s="16" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H3" s="17" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="I3" s="16" t="s">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="J3" s="18"/>
       <c r="K3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="16" t="s">
-        <v>29</v>
-      </c>
       <c r="M3" s="16" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="N3" s="16" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="O3" s="16"/>
     </row>
-    <row r="4" spans="1:15" ht="327" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="39"/>
-      <c r="B4" s="38"/>
+    <row r="4" spans="1:15" ht="327" customHeight="1">
+      <c r="A4" s="35"/>
+      <c r="B4" s="34"/>
       <c r="C4" s="6" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="D4" s="14"/>
-      <c r="E4" s="12"/>
+      <c r="E4" s="12" t="s">
+        <v>65</v>
+      </c>
       <c r="F4" s="6" t="s">
-        <v>112</v>
+        <v>11</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="I4" s="6"/>
       <c r="J4" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="K4" s="6" t="s">
-        <v>60</v>
-      </c>
       <c r="L4" s="6" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>27</v>
+        <v>69</v>
       </c>
       <c r="N4" s="6" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
@@ -3816,9 +3773,12 @@
     <mergeCell ref="B2:B4"/>
     <mergeCell ref="A2:A4"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="E4" r:id="rId1" xr:uid="{CB6C2776-D7AB-411A-9922-84A8C92D7D53}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -3828,82 +3788,82 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:O4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="88.81640625" customWidth="1"/>
-    <col min="3" max="3" width="31.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="103.81640625" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="88.7109375" customWidth="1"/>
+    <col min="3" max="3" width="31.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="103.7109375" customWidth="1"/>
     <col min="5" max="5" width="20" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.36328125" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26.28515625" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="57" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="64.54296875" customWidth="1"/>
-    <col min="11" max="11" width="42.54296875" customWidth="1"/>
-    <col min="12" max="12" width="4.1796875" customWidth="1"/>
-    <col min="13" max="13" width="15.1796875" customWidth="1"/>
-    <col min="14" max="14" width="58.453125" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="64.5703125" customWidth="1"/>
+    <col min="11" max="11" width="42.5703125" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="15.28515625" customWidth="1"/>
+    <col min="14" max="14" width="58.42578125" customWidth="1"/>
     <col min="15" max="15" width="63" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="28.9">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="N1" s="2" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O1" s="2" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:15" s="20" customFormat="1" ht="29" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" s="20" customFormat="1" ht="28.9" customHeight="1">
       <c r="A2" s="40">
         <v>1</v>
       </c>
       <c r="B2" s="43"/>
       <c r="C2" s="43" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>56</v>
+        <v>73</v>
       </c>
       <c r="E2" s="47"/>
       <c r="F2" s="47"/>
@@ -3917,59 +3877,59 @@
       <c r="N2" s="47"/>
       <c r="O2" s="48"/>
     </row>
-    <row r="3" spans="1:15" ht="343.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="343.5" customHeight="1">
       <c r="A3" s="41"/>
       <c r="B3" s="44"/>
       <c r="C3" s="44"/>
       <c r="D3" s="6" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="E3" s="50"/>
-      <c r="F3" s="39" t="s">
-        <v>113</v>
-      </c>
-      <c r="G3" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="39" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="39"/>
-      <c r="J3" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="K3" s="39" t="s">
-        <v>60</v>
-      </c>
-      <c r="L3" s="39" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="39" t="s">
-        <v>40</v>
+      <c r="F3" s="35" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="35" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="I3" s="35"/>
+      <c r="J3" s="35" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="35" t="s">
+        <v>68</v>
+      </c>
+      <c r="M3" s="35" t="s">
+        <v>77</v>
       </c>
       <c r="N3" s="49" t="s">
-        <v>111</v>
-      </c>
-      <c r="O3" s="39" t="s">
-        <v>65</v>
+        <v>78</v>
+      </c>
+      <c r="O3" s="35" t="s">
+        <v>79</v>
       </c>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15">
       <c r="A4" s="42"/>
       <c r="B4" s="45"/>
       <c r="C4" s="45"/>
       <c r="D4" s="6"/>
       <c r="E4" s="50"/>
-      <c r="F4" s="39"/>
-      <c r="G4" s="39"/>
-      <c r="H4" s="39"/>
-      <c r="I4" s="39"/>
-      <c r="J4" s="39"/>
-      <c r="K4" s="39"/>
-      <c r="L4" s="39"/>
-      <c r="M4" s="39"/>
+      <c r="F4" s="35"/>
+      <c r="G4" s="35"/>
+      <c r="H4" s="35"/>
+      <c r="I4" s="35"/>
+      <c r="J4" s="35"/>
+      <c r="K4" s="35"/>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
       <c r="N4" s="49"/>
-      <c r="O4" s="39"/>
+      <c r="O4" s="35"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -4001,226 +3961,226 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="146.54296875" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="84.1796875" customWidth="1"/>
-    <col min="5" max="5" width="24.1796875" customWidth="1"/>
-    <col min="6" max="6" width="29.90625" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="87.7265625" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="73.81640625" customWidth="1"/>
-    <col min="12" max="12" width="4.1796875" customWidth="1"/>
-    <col min="13" max="13" width="16.81640625" customWidth="1"/>
-    <col min="14" max="14" width="32.81640625" customWidth="1"/>
-    <col min="15" max="15" width="53.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="146.5703125" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="84.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="29.85546875" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="87.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="73.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="14" max="14" width="32.7109375" customWidth="1"/>
+    <col min="15" max="15" width="53.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="28.9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="213.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:15" ht="213.75" customHeight="1">
       <c r="A2" s="40">
         <v>1</v>
       </c>
       <c r="B2" s="51"/>
       <c r="C2" s="6" t="s">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I2" s="6"/>
       <c r="J2" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="K2" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="N2" s="11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="275.64999999999998" customHeight="1">
       <c r="A3" s="42"/>
       <c r="B3" s="52"/>
       <c r="C3" s="6" t="s">
-        <v>42</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>30</v>
+        <v>86</v>
       </c>
       <c r="E3" s="21"/>
       <c r="F3" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="I3" s="21"/>
       <c r="J3" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="K3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="6" t="s">
-        <v>29</v>
-      </c>
       <c r="M3" s="6" t="s">
-        <v>29</v>
+        <v>60</v>
       </c>
       <c r="N3" s="21"/>
       <c r="O3" s="6" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="408.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" ht="408.4" customHeight="1">
       <c r="A4" s="6">
         <v>2</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="6" t="s">
-        <v>31</v>
+        <v>89</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>32</v>
+        <v>90</v>
       </c>
       <c r="E4" s="21"/>
       <c r="F4" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="I4" s="21"/>
       <c r="J4" s="6" t="s">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="K4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="21" t="s">
+        <v>68</v>
+      </c>
+      <c r="M4" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="M4" s="21" t="s">
-        <v>29</v>
-      </c>
       <c r="N4" s="11" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="O4" s="21" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="409" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" ht="409.15" customHeight="1">
       <c r="A5" s="7">
         <v>3</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="6" t="s">
-        <v>80</v>
+        <v>92</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>81</v>
+        <v>93</v>
       </c>
       <c r="E5" s="7"/>
       <c r="F5" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="I5" s="7"/>
       <c r="J5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="M5" s="21" t="s">
+        <v>60</v>
+      </c>
+      <c r="N5" s="11" t="s">
         <v>83</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="M5" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="11" t="s">
-        <v>75</v>
       </c>
       <c r="O5" s="7"/>
     </row>
@@ -4241,114 +4201,114 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:O3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="51.1796875" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.1796875" customWidth="1"/>
-    <col min="5" max="5" width="24.1796875" customWidth="1"/>
-    <col min="6" max="6" width="27.453125" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="46.81640625" customWidth="1"/>
-    <col min="9" max="9" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="63.81640625" customWidth="1"/>
-    <col min="11" max="11" width="49.6328125" customWidth="1"/>
-    <col min="12" max="12" width="4.36328125" customWidth="1"/>
-    <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="58.90625" customWidth="1"/>
-    <col min="15" max="15" width="53.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.28515625" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.28515625" customWidth="1"/>
+    <col min="5" max="5" width="24.28515625" customWidth="1"/>
+    <col min="6" max="6" width="27.42578125" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="46.7109375" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="63.7109375" customWidth="1"/>
+    <col min="11" max="11" width="49.7109375" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="58.85546875" customWidth="1"/>
+    <col min="15" max="15" width="53.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" ht="28.9">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="5" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1" s="5" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>24</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="2" spans="1:15" ht="284.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="39"/>
-      <c r="B2" s="38"/>
+    <row r="2" spans="1:15" ht="284.64999999999998" customHeight="1">
+      <c r="A2" s="35"/>
+      <c r="B2" s="34"/>
       <c r="C2" s="53" t="s">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="D2" s="53" t="s">
-        <v>45</v>
+        <v>98</v>
       </c>
       <c r="E2" s="55"/>
       <c r="F2" s="53" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G2" s="53" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" s="53" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="I2" s="53"/>
       <c r="J2" s="53" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="K2" s="53" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L2" s="53" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="M2" s="53" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="N2" s="53" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="O2" s="40" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:15" ht="275.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="39"/>
-      <c r="B3" s="38"/>
+    <row r="3" spans="1:15" ht="275.64999999999998" customHeight="1">
+      <c r="A3" s="35"/>
+      <c r="B3" s="34"/>
       <c r="C3" s="54"/>
       <c r="D3" s="54"/>
       <c r="E3" s="56"/>
@@ -4393,199 +4353,199 @@
     <tabColor rgb="FF92D050"/>
   </sheetPr>
   <dimension ref="A1:Q4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="3.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="61.54296875" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="73.1796875" customWidth="1"/>
-    <col min="5" max="5" width="32.54296875" customWidth="1"/>
-    <col min="6" max="6" width="24.81640625" customWidth="1"/>
-    <col min="7" max="7" width="7.81640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="49.453125" customWidth="1"/>
-    <col min="9" max="9" width="39.1796875" customWidth="1"/>
-    <col min="10" max="10" width="51.1796875" customWidth="1"/>
-    <col min="11" max="11" width="48.54296875" customWidth="1"/>
-    <col min="12" max="12" width="4.1796875" customWidth="1"/>
-    <col min="13" max="13" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="32.81640625" customWidth="1"/>
-    <col min="15" max="15" width="53.453125" customWidth="1"/>
+    <col min="1" max="1" width="3.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="61.5703125" customWidth="1"/>
+    <col min="3" max="3" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="73.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.5703125" customWidth="1"/>
+    <col min="6" max="6" width="24.7109375" customWidth="1"/>
+    <col min="7" max="7" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49.42578125" customWidth="1"/>
+    <col min="9" max="9" width="39.28515625" customWidth="1"/>
+    <col min="10" max="10" width="51.28515625" customWidth="1"/>
+    <col min="11" max="11" width="48.5703125" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" customWidth="1"/>
+    <col min="13" max="13" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="32.7109375" customWidth="1"/>
+    <col min="15" max="15" width="53.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>14</v>
+        <v>43</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>15</v>
+        <v>44</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>20</v>
+        <v>49</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="M1" s="4" t="s">
-        <v>22</v>
+        <v>51</v>
       </c>
       <c r="N1" s="4" t="s">
-        <v>23</v>
+        <v>52</v>
       </c>
       <c r="O1" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="P1" s="8"/>
       <c r="Q1" s="8"/>
     </row>
-    <row r="2" spans="1:17" ht="130.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" ht="129.6">
       <c r="A2" s="18">
         <v>1</v>
       </c>
       <c r="B2" s="57"/>
       <c r="C2" s="18" t="s">
-        <v>34</v>
+        <v>102</v>
       </c>
       <c r="D2" s="18"/>
       <c r="E2" s="26" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>12</v>
+        <v>36</v>
       </c>
       <c r="H2" s="18" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="I2" s="18" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="J2" s="18" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="K2" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="L2" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="L2" s="18" t="s">
-        <v>29</v>
-      </c>
       <c r="M2" s="18" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="N2" s="18" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="O2" s="18" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="205" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" ht="205.15" customHeight="1">
       <c r="A3" s="18">
         <v>2</v>
       </c>
       <c r="B3" s="57"/>
       <c r="C3" s="18" t="s">
-        <v>35</v>
+        <v>107</v>
       </c>
       <c r="D3" s="27"/>
       <c r="E3" s="28" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="I3" s="18" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="J3" s="18" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="K3" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="18" t="s">
-        <v>29</v>
-      </c>
       <c r="M3" s="18" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="N3" s="18" t="s">
-        <v>47</v>
+        <v>106</v>
       </c>
       <c r="O3" s="18" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="150" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" ht="150" customHeight="1">
       <c r="A4" s="16">
         <v>3</v>
       </c>
       <c r="B4" s="57"/>
       <c r="C4" s="18" t="s">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="D4" s="16"/>
       <c r="E4" s="29" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>113</v>
+        <v>13</v>
       </c>
       <c r="G4" s="16" t="s">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="I4" s="16"/>
       <c r="J4" s="18" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="K4" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="L4" s="18" t="s">
-        <v>29</v>
-      </c>
       <c r="M4" s="18" t="s">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="N4" s="18" t="s">
         <v>106</v>
       </c>
       <c r="O4" s="18" t="s">
-        <v>107</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -4613,19 +4573,19 @@
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="88ca0028-d944-4b54-a24a-33c956642033">
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="eb43bdf0-3619-4b54-b31e-a8a72f171391">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="aef3f498-749b-43cd-ac3b-f8654dcba8c2" xsi:nil="true"/>
+    <TaxCatchAll xmlns="2dadf7ee-14cc-45f3-948a-a38a0e838d24" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005A3C49B5B8A2D749BAFDCDB853B21597" ma:contentTypeVersion="12" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="a6cc039eb631fd7d2f6ba3af9d26378a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="88ca0028-d944-4b54-a24a-33c956642033" xmlns:ns3="aef3f498-749b-43cd-ac3b-f8654dcba8c2" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d362f1f0b652b2f2d438f5707b209cbb" ns2:_="" ns3:_="">
-    <xsd:import namespace="88ca0028-d944-4b54-a24a-33c956642033"/>
-    <xsd:import namespace="aef3f498-749b-43cd-ac3b-f8654dcba8c2"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A9B4981540F375498654EAFF3F046281" ma:contentTypeVersion="11" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="8a5ebea04648d29e8f47710243b77275">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="eb43bdf0-3619-4b54-b31e-a8a72f171391" xmlns:ns3="2dadf7ee-14cc-45f3-948a-a38a0e838d24" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9d8d4f3bc4cf75db31872049f5cbc23a" ns2:_="" ns3:_="">
+    <xsd:import namespace="eb43bdf0-3619-4b54-b31e-a8a72f171391"/>
+    <xsd:import namespace="2dadf7ee-14cc-45f3-948a-a38a0e838d24"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -4642,7 +4602,6 @@
                 <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
                 <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -4650,7 +4609,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="88ca0028-d944-4b54-a24a-33c956642033" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="eb43bdf0-3619-4b54-b31e-a8a72f171391" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -4702,16 +4661,11 @@
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="aef3f498-749b-43cd-ac3b-f8654dcba8c2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="2dadf7ee-14cc-45f3-948a-a38a0e838d24" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{cdc93b2a-8661-4444-939a-2cf5c9f51721}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="aef3f498-749b-43cd-ac3b-f8654dcba8c2">
+    <xsd:element name="TaxCatchAll" ma:index="17" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{bc5e150e-238a-448e-9cab-ff45677664b7}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="2dadf7ee-14cc-45f3-948a-a38a0e838d24">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:MultiChoiceLookup">
@@ -4823,47 +4777,15 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6217EDB1-CF7F-45C6-A629-8BC0BA3054C0}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6217EDB1-CF7F-45C6-A629-8BC0BA3054C0}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A222457-EE3E-4D36-A01B-F5B85C181035}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="aef3f498-749b-43cd-ac3b-f8654dcba8c2"/>
-    <ds:schemaRef ds:uri="88ca0028-d944-4b54-a24a-33c956642033"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1A222457-EE3E-4D36-A01B-F5B85C181035}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1C3775BC-9AB2-4DBB-A274-E768B4BD633D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="88ca0028-d944-4b54-a24a-33c956642033"/>
-    <ds:schemaRef ds:uri="aef3f498-749b-43cd-ac3b-f8654dcba8c2"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{65EA2E83-5502-4639-A07A-15D53139B65E}"/>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
